--- a/data/dsc_cane_shifting.xlsx
+++ b/data/dsc_cane_shifting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -28,6 +28,21 @@
     <t>Laborers</t>
   </si>
   <si>
+    <t>Capitao</t>
+  </si>
+  <si>
+    <t>Dipper</t>
+  </si>
+  <si>
+    <t>B/Guard</t>
+  </si>
+  <si>
+    <t>First_Aider</t>
+  </si>
+  <si>
+    <t>SHEQ</t>
+  </si>
+  <si>
     <t>2025-05-05</t>
   </si>
   <si>
@@ -40,13 +55,22 @@
     <t>2025-07-01</t>
   </si>
   <si>
-    <t>1111</t>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>4415</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>38</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -404,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,10 +444,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>5412</v>
@@ -435,9 +474,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>5290</v>
@@ -449,9 +488,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>5601</v>
@@ -463,18 +502,47 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>1111</v>
+      </c>
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
+      <c r="D5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_shifting.xlsx
+++ b/data/dsc_cane_shifting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -46,28 +46,73 @@
     <t>2025-05-05</t>
   </si>
   <si>
-    <t>2025-06-10</t>
-  </si>
-  <si>
-    <t>2025-06-25</t>
-  </si>
-  <si>
-    <t>2025-07-01</t>
-  </si>
-  <si>
-    <t>2025-07-25</t>
-  </si>
-  <si>
-    <t>4415</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>34</t>
+    <t>2025-05-06</t>
+  </si>
+  <si>
+    <t>2025-05-11</t>
+  </si>
+  <si>
+    <t>2025-05-13</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>2025-05-16</t>
+  </si>
+  <si>
+    <t>2025-05-20</t>
+  </si>
+  <si>
+    <t>2025-05-22</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>DG25000</t>
+  </si>
+  <si>
+    <t>5219</t>
+  </si>
+  <si>
+    <t>DG04002</t>
+  </si>
+  <si>
+    <t>DG04003</t>
+  </si>
+  <si>
+    <t>DG04004</t>
+  </si>
+  <si>
+    <t>DG04005</t>
+  </si>
+  <si>
+    <t>DG25005</t>
+  </si>
+  <si>
+    <t>DG25006</t>
+  </si>
+  <si>
+    <t>DG27004</t>
+  </si>
+  <si>
+    <t>DG27003</t>
+  </si>
+  <si>
+    <t>DG11003</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>0</t>
@@ -428,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -465,13 +510,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>5412</v>
+        <v>2405</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>175</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -479,13 +539,28 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>5290</v>
+        <v>2405</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>73</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -493,13 +568,28 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>5601</v>
+        <v>2207</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>187</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -507,42 +597,434 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>1111</v>
+        <v>2207</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>246</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>2207</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>338</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7">
+        <v>2207</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>115</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>2207</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>115</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>63</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>135</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="D11">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>35</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_shifting.xlsx
+++ b/data/dsc_cane_shifting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
@@ -70,6 +70,21 @@
     <t>2025-05-29</t>
   </si>
   <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
     <t>DG25000</t>
   </si>
   <si>
@@ -103,16 +118,22 @@
     <t>DG11003</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>4415</t>
+  </si>
+  <si>
+    <t>4317</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>89</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>0</t>
@@ -473,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -713,7 +734,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>18</v>
@@ -742,7 +763,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>19</v>
@@ -771,7 +792,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>17</v>
@@ -800,7 +821,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -829,7 +850,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -858,7 +879,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -887,7 +908,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -916,7 +937,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -945,7 +966,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -974,7 +995,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1003,28 +1024,173 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>20</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21">
         <v>30</v>
       </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" t="s">
-        <v>33</v>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>43</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_cane_shifting.xlsx
+++ b/data/dsc_cane_shifting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -85,6 +85,24 @@
     <t>2025-08-08</t>
   </si>
   <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-13</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>2025-11-15</t>
+  </si>
+  <si>
+    <t>2025-11-16</t>
+  </si>
+  <si>
+    <t>2025-11-22</t>
+  </si>
+  <si>
     <t>DG25000</t>
   </si>
   <si>
@@ -127,16 +145,46 @@
     <t>2403</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>DG09006</t>
+  </si>
+  <si>
+    <t>DG09007</t>
+  </si>
+  <si>
+    <t>DG09008</t>
+  </si>
+  <si>
+    <t>DG09009</t>
+  </si>
+  <si>
+    <t>3412</t>
+  </si>
+  <si>
+    <t>5632</t>
+  </si>
+  <si>
+    <t>DG09010</t>
+  </si>
+  <si>
+    <t>4314</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -494,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -734,7 +782,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>18</v>
@@ -763,7 +811,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>19</v>
@@ -792,7 +840,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>17</v>
@@ -821,7 +869,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -850,7 +898,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -879,7 +927,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -908,7 +956,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -937,7 +985,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -966,7 +1014,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -995,7 +1043,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1024,7 +1072,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1053,7 +1101,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -1082,7 +1130,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>15</v>
@@ -1111,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>15</v>
@@ -1140,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C23">
         <v>11</v>
@@ -1169,28 +1217,492 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>89</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D25">
+        <v>278</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>260</v>
+      </c>
+      <c r="E26">
+        <v>7</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>67</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>57</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30">
+        <v>32</v>
+      </c>
+      <c r="D30">
+        <v>218</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>22</v>
+      </c>
+      <c r="D31">
+        <v>66</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32">
+        <v>36</v>
+      </c>
+      <c r="D32">
+        <v>96</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33">
+        <v>12</v>
+      </c>
+      <c r="D33">
+        <v>54</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34">
+        <v>17</v>
+      </c>
+      <c r="D34">
+        <v>126</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35">
         <v>37</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36">
+        <v>25</v>
+      </c>
+      <c r="D36">
+        <v>204</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37">
         <v>38</v>
       </c>
-      <c r="E24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" t="s">
-        <v>40</v>
+      <c r="D37">
+        <v>217</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>7</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>33</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39">
+        <v>31</v>
+      </c>
+      <c r="D39">
+        <v>223</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" t="s">
+        <v>56</v>
+      </c>
+      <c r="I40" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
